--- a/AAII_Financials/Quarterly/GWSO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GWSO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>GWSO</t>
   </si>
@@ -656,84 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
@@ -774,13 +778,16 @@
         <v>100</v>
       </c>
       <c r="P8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,14 +815,14 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
+      <c r="L9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -826,8 +833,11 @@
       <c r="Q9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -855,26 +865,29 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
+      <c r="L10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
       <c r="N10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3">
         <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,37 +905,38 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
+        <v>100</v>
+      </c>
+      <c r="G12" s="3">
         <v>300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
-        <v>100</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>4</v>
+      <c r="I12" s="3">
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
+      <c r="K12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>4</v>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -997,8 +1017,8 @@
       <c r="E14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,8 +1122,9 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1105,13 +1132,13 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>300</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
@@ -1120,31 +1147,34 @@
         <v>300</v>
       </c>
       <c r="J17" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L17" s="3">
         <v>200</v>
       </c>
       <c r="M17" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N17" s="3">
+        <v>100</v>
+      </c>
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
-        <v>100</v>
-      </c>
       <c r="P17" s="3">
         <v>100</v>
       </c>
       <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1152,13 +1182,13 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-300</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
@@ -1167,31 +1197,34 @@
         <v>-300</v>
       </c>
       <c r="J18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-200</v>
       </c>
       <c r="L18" s="3">
         <v>-200</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
       <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,8 +1242,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1221,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1242,22 +1276,25 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1265,13 +1302,13 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-300</v>
       </c>
       <c r="H21" s="3">
         <v>-300</v>
@@ -1280,31 +1317,34 @@
         <v>-300</v>
       </c>
       <c r="J21" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="K21" s="3">
         <v>-100</v>
       </c>
       <c r="L21" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="M21" s="3">
         <v>-200</v>
       </c>
       <c r="N21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
       <c r="P21" s="3">
         <v>0</v>
       </c>
       <c r="Q21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1317,8 +1357,8 @@
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
@@ -1335,8 +1375,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1350,8 +1390,11 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1359,13 +1402,13 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-300</v>
       </c>
       <c r="H23" s="3">
         <v>-300</v>
@@ -1374,10 +1417,10 @@
         <v>-300</v>
       </c>
       <c r="J23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-100</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-200</v>
       </c>
       <c r="L23" s="3">
         <v>-200</v>
@@ -1386,19 +1429,22 @@
         <v>-200</v>
       </c>
       <c r="N23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
       <c r="Q23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,8 +1540,11 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1500,13 +1552,13 @@
         <v>-100</v>
       </c>
       <c r="E26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-300</v>
       </c>
       <c r="H26" s="3">
         <v>-300</v>
@@ -1515,10 +1567,10 @@
         <v>-300</v>
       </c>
       <c r="J26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-200</v>
       </c>
       <c r="L26" s="3">
         <v>-200</v>
@@ -1527,19 +1579,22 @@
         <v>-200</v>
       </c>
       <c r="N26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
       <c r="Q26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1547,13 +1602,13 @@
         <v>-100</v>
       </c>
       <c r="E27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-300</v>
       </c>
       <c r="H27" s="3">
         <v>-300</v>
@@ -1562,10 +1617,10 @@
         <v>-300</v>
       </c>
       <c r="J27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-100</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-200</v>
       </c>
       <c r="L27" s="3">
         <v>-200</v>
@@ -1574,19 +1629,22 @@
         <v>-200</v>
       </c>
       <c r="N27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
       <c r="Q27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1690,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,8 +1840,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1785,14 +1855,14 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -1806,13 +1876,13 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -1820,8 +1890,11 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1829,13 +1902,13 @@
         <v>-100</v>
       </c>
       <c r="E33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-300</v>
       </c>
       <c r="H33" s="3">
         <v>-300</v>
@@ -1844,10 +1917,10 @@
         <v>-300</v>
       </c>
       <c r="J33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-200</v>
       </c>
       <c r="L33" s="3">
         <v>-200</v>
@@ -1856,19 +1929,22 @@
         <v>-200</v>
       </c>
       <c r="N33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
       <c r="Q33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,8 +1990,11 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1923,13 +2002,13 @@
         <v>-100</v>
       </c>
       <c r="E35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-300</v>
       </c>
       <c r="H35" s="3">
         <v>-300</v>
@@ -1938,10 +2017,10 @@
         <v>-300</v>
       </c>
       <c r="J35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-200</v>
       </c>
       <c r="L35" s="3">
         <v>-200</v>
@@ -1950,71 +2029,77 @@
         <v>-200</v>
       </c>
       <c r="N35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
       <c r="Q35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,13 +2137,14 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
@@ -2069,26 +2156,26 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>4</v>
       </c>
@@ -2098,8 +2185,11 @@
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2110,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>100</v>
@@ -2121,8 +2211,8 @@
       <c r="I42" s="3">
         <v>100</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
+      <c r="J42" s="3">
+        <v>100</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>4</v>
@@ -2136,8 +2226,8 @@
       <c r="N42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2145,31 +2235,34 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2192,8 +2285,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2221,14 +2317,14 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>4</v>
@@ -2239,8 +2335,11 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2254,7 +2353,7 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -2272,10 +2371,10 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>100</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>4</v>
@@ -2286,44 +2385,47 @@
       <c r="Q45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E46" s="3">
         <v>100</v>
       </c>
       <c r="F46" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G46" s="3">
         <v>200</v>
       </c>
       <c r="H46" s="3">
+        <v>200</v>
+      </c>
+      <c r="I46" s="3">
         <v>400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>4</v>
       </c>
@@ -2333,8 +2435,11 @@
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2365,8 +2470,8 @@
       <c r="L47" s="3">
         <v>100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
+      <c r="M47" s="3">
+        <v>100</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>4</v>
@@ -2380,8 +2485,11 @@
       <c r="Q47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2407,16 +2515,16 @@
         <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3">
         <v>100</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>4</v>
@@ -2427,8 +2535,11 @@
       <c r="Q48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2460,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>100</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>100</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>4</v>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,13 +2685,16 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -2603,8 +2723,8 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,43 +2785,46 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E54" s="3">
         <v>200</v>
       </c>
       <c r="F54" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G54" s="3">
         <v>300</v>
       </c>
       <c r="H54" s="3">
+        <v>300</v>
+      </c>
+      <c r="I54" s="3">
         <v>600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>800</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1000</v>
       </c>
       <c r="M54" s="3">
         <v>1000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
+      <c r="N54" s="3">
+        <v>1000</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>4</v>
@@ -2709,8 +2835,11 @@
       <c r="Q54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,8 +2877,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2759,7 +2890,7 @@
         <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
@@ -2782,8 +2913,8 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
+      <c r="N57" s="3">
+        <v>0</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>4</v>
@@ -2794,23 +2925,26 @@
       <c r="Q57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
       </c>
       <c r="F58" s="3">
+        <v>400</v>
+      </c>
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2826,8 +2960,8 @@
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2841,8 +2975,11 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2856,7 +2993,7 @@
         <v>100</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
         <v>0</v>
@@ -2876,8 +3013,8 @@
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
@@ -2888,23 +3025,26 @@
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>400</v>
       </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
       <c r="H60" s="3">
         <v>0</v>
       </c>
@@ -2923,8 +3063,8 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
+      <c r="N60" s="3">
+        <v>0</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>4</v>
@@ -2935,8 +3075,11 @@
       <c r="Q60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2982,19 +3125,22 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
+      <c r="F62" s="3">
+        <v>0</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>4</v>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,23 +3325,26 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>500</v>
+      </c>
+      <c r="E66" s="3">
         <v>600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>400</v>
       </c>
-      <c r="G66" s="3">
-        <v>0</v>
-      </c>
       <c r="H66" s="3">
         <v>0</v>
       </c>
@@ -3205,8 +3363,8 @@
       <c r="M66" s="3">
         <v>0</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
+      <c r="N66" s="3">
+        <v>0</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>4</v>
@@ -3217,8 +3375,11 @@
       <c r="Q66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,44 +3595,47 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-4700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-4400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
@@ -3471,8 +3645,11 @@
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,43 +3795,46 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>800</v>
-      </c>
-      <c r="L76" s="3">
-        <v>1000</v>
       </c>
       <c r="M76" s="3">
         <v>1000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>4</v>
+      <c r="N76" s="3">
+        <v>1000</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>4</v>
@@ -3659,8 +3845,11 @@
       <c r="Q76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,60 +3895,66 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3767,13 +3962,13 @@
         <v>-100</v>
       </c>
       <c r="E81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-300</v>
       </c>
       <c r="H81" s="3">
         <v>-300</v>
@@ -3782,10 +3977,10 @@
         <v>-300</v>
       </c>
       <c r="J81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-200</v>
       </c>
       <c r="L81" s="3">
         <v>-200</v>
@@ -3794,19 +3989,22 @@
         <v>-200</v>
       </c>
       <c r="N81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
       <c r="Q81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,19 +4320,22 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-300</v>
       </c>
       <c r="G89" s="3">
         <v>-300</v>
@@ -4130,20 +4347,20 @@
         <v>-300</v>
       </c>
       <c r="J89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="K89" s="3">
         <v>-100</v>
       </c>
       <c r="L89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
@@ -4153,8 +4370,11 @@
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4207,8 +4428,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4540,11 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4343,16 +4573,16 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -4360,8 +4590,11 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,44 +4810,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>4</v>
       </c>
@@ -4614,8 +4860,11 @@
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,13 +4910,16 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
@@ -4676,29 +4928,29 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-300</v>
       </c>
       <c r="I102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-100</v>
       </c>
       <c r="L102" s="3">
         <v>-100</v>
       </c>
       <c r="M102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
@@ -4706,6 +4958,9 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GWSO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GWSO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>GWSO</t>
   </si>
@@ -656,88 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,22 +779,28 @@
         <v>0</v>
       </c>
       <c r="N8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -818,17 +831,17 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3">
-        <v>100</v>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
@@ -836,8 +849,14 @@
       <c r="R9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -868,26 +887,32 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0</v>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,43 +931,45 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>100</v>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
-        <v>100</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
+      <c r="K12" s="3">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>4</v>
+      <c r="N12" s="3">
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>4</v>
@@ -956,8 +983,14 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,8 +1039,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1020,11 +1059,11 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1056,8 +1095,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1151,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,8 +1174,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1132,49 +1185,55 @@
         <v>100</v>
       </c>
       <c r="E17" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H17" s="3">
         <v>300</v>
       </c>
       <c r="I17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
       <c r="K17" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
+        <v>100</v>
+      </c>
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
-        <v>100</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>100</v>
-      </c>
       <c r="R17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="S17" s="3">
+        <v>100</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1182,49 +1241,55 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-300</v>
-      </c>
       <c r="G18" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
         <v>-300</v>
       </c>
       <c r="I18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
       <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1308,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1252,22 +1319,22 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1279,22 +1346,28 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,49 +1375,55 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-300</v>
       </c>
       <c r="J21" s="3">
         <v>-300</v>
       </c>
       <c r="K21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1360,11 +1439,11 @@
       <c r="G22" s="3">
         <v>0</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>4</v>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>4</v>
@@ -1378,11 +1457,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1393,8 +1472,14 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1402,49 +1487,55 @@
         <v>-100</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
-        <v>-300</v>
-      </c>
       <c r="G23" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H23" s="3">
         <v>-300</v>
       </c>
       <c r="I23" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J23" s="3">
         <v>-300</v>
       </c>
       <c r="K23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3">
         <v>-100</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-200</v>
       </c>
       <c r="N23" s="3">
         <v>-200</v>
       </c>
       <c r="O23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1493,8 +1584,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,8 +1640,14 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1552,49 +1655,55 @@
         <v>-100</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
-        <v>-300</v>
-      </c>
       <c r="G26" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H26" s="3">
         <v>-300</v>
       </c>
       <c r="I26" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J26" s="3">
         <v>-300</v>
       </c>
       <c r="K26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M26" s="3">
         <v>-100</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-200</v>
       </c>
       <c r="N26" s="3">
         <v>-200</v>
       </c>
       <c r="O26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1602,49 +1711,55 @@
         <v>-100</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-300</v>
-      </c>
       <c r="G27" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H27" s="3">
         <v>-300</v>
       </c>
       <c r="I27" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J27" s="3">
         <v>-300</v>
       </c>
       <c r="K27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M27" s="3">
         <v>-100</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-200</v>
       </c>
       <c r="N27" s="3">
         <v>-200</v>
       </c>
       <c r="O27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1808,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1864,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1920,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,8 +1976,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1852,23 +1991,23 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -1879,22 +2018,28 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
-        <v>100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1902,49 +2047,55 @@
         <v>-100</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-300</v>
-      </c>
       <c r="G33" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H33" s="3">
         <v>-300</v>
       </c>
       <c r="I33" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J33" s="3">
         <v>-300</v>
       </c>
       <c r="K33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M33" s="3">
         <v>-100</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-200</v>
       </c>
       <c r="N33" s="3">
         <v>-200</v>
       </c>
       <c r="O33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,8 +2144,14 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2002,104 +2159,116 @@
         <v>-100</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-300</v>
-      </c>
       <c r="G35" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H35" s="3">
         <v>-300</v>
       </c>
       <c r="I35" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J35" s="3">
         <v>-300</v>
       </c>
       <c r="K35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M35" s="3">
         <v>-100</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-200</v>
       </c>
       <c r="N35" s="3">
         <v>-200</v>
       </c>
       <c r="O35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2287,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,19 +2309,21 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41" s="3">
         <v>0</v>
@@ -2159,13 +2332,13 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>400</v>
-      </c>
-      <c r="J41" s="3">
-        <v>700</v>
-      </c>
-      <c r="K41" s="3">
-        <v>800</v>
       </c>
       <c r="L41" s="3">
         <v>700</v>
@@ -2174,22 +2347,28 @@
         <v>800</v>
       </c>
       <c r="N41" s="3">
+        <v>700</v>
+      </c>
+      <c r="O41" s="3">
+        <v>800</v>
+      </c>
+      <c r="P41" s="3">
         <v>900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2203,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>100</v>
@@ -2214,11 +2393,11 @@
       <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
+      <c r="K42" s="3">
+        <v>100</v>
+      </c>
+      <c r="L42" s="3">
+        <v>100</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
@@ -2229,28 +2408,34 @@
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
+        <v>100</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>4</v>
@@ -2264,11 +2449,11 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2288,8 +2473,14 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2320,8 +2511,8 @@
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2329,8 +2520,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>4</v>
+      <c r="P44" s="3">
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>4</v>
@@ -2338,13 +2529,19 @@
       <c r="R44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -2356,10 +2553,10 @@
         <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -2374,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="N45" s="3">
-        <v>100</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
+        <v>100</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>4</v>
@@ -2388,34 +2585,40 @@
       <c r="R45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>300</v>
+      </c>
+      <c r="E46" s="3">
         <v>200</v>
       </c>
-      <c r="E46" s="3">
-        <v>100</v>
-      </c>
       <c r="F46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G46" s="3">
+        <v>100</v>
+      </c>
+      <c r="H46" s="3">
+        <v>100</v>
+      </c>
+      <c r="I46" s="3">
         <v>200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>400</v>
-      </c>
-      <c r="J46" s="3">
-        <v>700</v>
-      </c>
-      <c r="K46" s="3">
-        <v>900</v>
       </c>
       <c r="L46" s="3">
         <v>700</v>
@@ -2424,30 +2627,36 @@
         <v>900</v>
       </c>
       <c r="N46" s="3">
+        <v>700</v>
+      </c>
+      <c r="O46" s="3">
+        <v>900</v>
+      </c>
+      <c r="P46" s="3">
         <v>1000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
@@ -2473,11 +2682,11 @@
       <c r="M47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
+      <c r="N47" s="3">
+        <v>100</v>
+      </c>
+      <c r="O47" s="3">
+        <v>100</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
@@ -2488,8 +2697,14 @@
       <c r="R47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2518,19 +2733,19 @@
         <v>0</v>
       </c>
       <c r="L48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="O48" s="3">
+        <v>100</v>
+      </c>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>4</v>
@@ -2538,8 +2753,14 @@
       <c r="R48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2574,13 +2795,13 @@
         <v>0</v>
       </c>
       <c r="N49" s="3">
-        <v>100</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>100</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
@@ -2588,8 +2809,14 @@
       <c r="R49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2865,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,19 +2921,25 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2726,11 +2965,11 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
@@ -2738,8 +2977,14 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,8 +3033,14 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -2800,37 +3051,37 @@
         <v>200</v>
       </c>
       <c r="F54" s="3">
+        <v>300</v>
+      </c>
+      <c r="G54" s="3">
         <v>200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>200</v>
+      </c>
+      <c r="I54" s="3">
         <v>300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>900</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>800</v>
       </c>
       <c r="M54" s="3">
         <v>1000</v>
       </c>
       <c r="N54" s="3">
+        <v>800</v>
+      </c>
+      <c r="O54" s="3">
         <v>1000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>4</v>
+      <c r="P54" s="3">
+        <v>1000</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>4</v>
@@ -2838,8 +3089,14 @@
       <c r="R54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +3115,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,25 +3137,27 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>0</v>
@@ -2916,11 +3177,11 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>4</v>
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>4</v>
@@ -2928,29 +3189,35 @@
       <c r="R57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
+        <v>300</v>
+      </c>
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>4</v>
       </c>
@@ -2963,11 +3230,11 @@
       <c r="M58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2978,16 +3245,22 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -2996,10 +3269,10 @@
         <v>100</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
@@ -3016,11 +3289,11 @@
       <c r="N59" s="3">
         <v>0</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3">
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
@@ -3028,29 +3301,35 @@
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E60" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F60" s="3">
         <v>500</v>
       </c>
       <c r="G60" s="3">
+        <v>600</v>
+      </c>
+      <c r="H60" s="3">
+        <v>500</v>
+      </c>
+      <c r="I60" s="3">
         <v>400</v>
       </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
       <c r="J60" s="3">
         <v>0</v>
       </c>
@@ -3066,11 +3345,11 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>4</v>
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>4</v>
@@ -3078,8 +3357,14 @@
       <c r="R60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3128,8 +3413,14 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3139,14 +3430,14 @@
       <c r="E62" s="3">
         <v>0</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>4</v>
@@ -3178,8 +3469,14 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3525,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3581,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,29 +3637,35 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E66" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F66" s="3">
         <v>500</v>
       </c>
       <c r="G66" s="3">
+        <v>600</v>
+      </c>
+      <c r="H66" s="3">
+        <v>500</v>
+      </c>
+      <c r="I66" s="3">
         <v>400</v>
       </c>
-      <c r="H66" s="3">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3">
-        <v>0</v>
-      </c>
       <c r="J66" s="3">
         <v>0</v>
       </c>
@@ -3366,11 +3681,11 @@
       <c r="N66" s="3">
         <v>0</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>4</v>
+      <c r="O66" s="3">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3">
+        <v>0</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>4</v>
@@ -3378,8 +3693,14 @@
       <c r="R66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3719,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3771,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3827,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3883,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3939,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="G72" s="3">
         <v>-5500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-5400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-5100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-4700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-4400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-4100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-3800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-3700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-3600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-3400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +4051,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +4107,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,34 +4163,40 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F76" s="3">
         <v>-200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>600</v>
-      </c>
-      <c r="J76" s="3">
-        <v>800</v>
-      </c>
-      <c r="K76" s="3">
-        <v>1000</v>
       </c>
       <c r="L76" s="3">
         <v>800</v>
@@ -3834,13 +4205,13 @@
         <v>1000</v>
       </c>
       <c r="N76" s="3">
+        <v>800</v>
+      </c>
+      <c r="O76" s="3">
         <v>1000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>4</v>
+      <c r="P76" s="3">
+        <v>1000</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>4</v>
@@ -3848,8 +4219,14 @@
       <c r="R76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,63 +4275,75 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3962,49 +4351,55 @@
         <v>-100</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-300</v>
-      </c>
       <c r="G81" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H81" s="3">
         <v>-300</v>
       </c>
       <c r="I81" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="J81" s="3">
         <v>-300</v>
       </c>
       <c r="K81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M81" s="3">
         <v>-100</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-200</v>
       </c>
       <c r="N81" s="3">
         <v>-200</v>
       </c>
       <c r="O81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4418,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4073,8 +4470,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4526,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4582,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4638,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4694,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,8 +4750,14 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4332,16 +4765,16 @@
         <v>-200</v>
       </c>
       <c r="E89" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F89" s="3">
         <v>-200</v>
       </c>
       <c r="G89" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H89" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="I89" s="3">
         <v>-300</v>
@@ -4350,22 +4783,22 @@
         <v>-300</v>
       </c>
       <c r="K89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M89" s="3">
         <v>-100</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-300</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
       <c r="O89" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="P89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -4373,8 +4806,14 @@
       <c r="R89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,8 +4832,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4431,11 +4872,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
@@ -4443,8 +4884,14 @@
       <c r="R91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4940,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,8 +4996,14 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4552,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -4576,25 +5035,31 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +5078,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4663,8 +5130,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +5186,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5242,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,58 +5298,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>100</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>300</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
       </c>
       <c r="M100" s="3">
         <v>300</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>300</v>
+      </c>
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4913,54 +5410,66 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>900</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GWSO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GWSO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>GWSO</t>
   </si>
@@ -656,118 +656,126 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -785,22 +793,28 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3">
         <v>100</v>
       </c>
       <c r="S8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -837,26 +851,32 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
       <c r="S9" s="3">
         <v>0</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -893,26 +913,32 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0</v>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,13 +959,15 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>4</v>
+      <c r="D12" s="3">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>4</v>
@@ -950,32 +978,32 @@
       <c r="G12" s="3">
         <v>0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0</v>
+      <c r="N12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>4</v>
+      <c r="P12" s="3">
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>4</v>
@@ -989,8 +1017,14 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,25 +1079,31 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1101,8 +1141,14 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1203,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1228,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="F17" s="3">
         <v>100</v>
       </c>
       <c r="G17" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H17" s="3">
         <v>100</v>
       </c>
-      <c r="H17" s="3">
-        <v>300</v>
-      </c>
       <c r="I17" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
       <c r="K17" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L17" s="3">
         <v>300</v>
       </c>
       <c r="M17" s="3">
+        <v>300</v>
+      </c>
+      <c r="N17" s="3">
+        <v>300</v>
+      </c>
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
-      </c>
-      <c r="P17" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>900</v>
       </c>
       <c r="R17" s="3">
         <v>100</v>
       </c>
       <c r="S17" s="3">
+        <v>900</v>
+      </c>
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3">
+        <v>100</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>0</v>
       </c>
       <c r="E18" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="F18" s="3">
         <v>-100</v>
       </c>
       <c r="G18" s="3">
+        <v>100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
       <c r="I18" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
       <c r="K18" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L18" s="3">
         <v>-300</v>
       </c>
       <c r="M18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1376,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1319,111 +1387,123 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="L20" s="3">
+        <v>100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F21" s="3">
         <v>-100</v>
       </c>
       <c r="G21" s="3">
+        <v>100</v>
+      </c>
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="H21" s="3">
-        <v>-200</v>
-      </c>
       <c r="I21" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J21" s="3">
         <v>-300</v>
       </c>
       <c r="K21" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L21" s="3">
         <v>-300</v>
       </c>
       <c r="M21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
       <c r="T21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1445,11 +1525,11 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>4</v>
@@ -1463,11 +1543,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1478,87 +1558,99 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F23" s="3">
         <v>-100</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>-300</v>
-      </c>
       <c r="I23" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J23" s="3">
         <v>-300</v>
       </c>
       <c r="K23" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L23" s="3">
         <v>-300</v>
       </c>
       <c r="M23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O23" s="3">
         <v>-100</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-200</v>
       </c>
       <c r="P23" s="3">
         <v>-200</v>
       </c>
       <c r="Q23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1590,8 +1682,14 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1744,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F26" s="3">
         <v>-100</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>-300</v>
-      </c>
       <c r="I26" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J26" s="3">
         <v>-300</v>
       </c>
       <c r="K26" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L26" s="3">
         <v>-300</v>
       </c>
       <c r="M26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O26" s="3">
         <v>-100</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-200</v>
       </c>
       <c r="P26" s="3">
         <v>-200</v>
       </c>
       <c r="Q26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F27" s="3">
         <v>-100</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>-300</v>
-      </c>
       <c r="I27" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J27" s="3">
         <v>-300</v>
       </c>
       <c r="K27" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L27" s="3">
         <v>-300</v>
       </c>
       <c r="M27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O27" s="3">
         <v>-100</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-200</v>
       </c>
       <c r="P27" s="3">
         <v>-200</v>
       </c>
       <c r="Q27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1930,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1992,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2054,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2116,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1991,111 +2131,123 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="L32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>200</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F33" s="3">
         <v>-100</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>-300</v>
-      </c>
       <c r="I33" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J33" s="3">
         <v>-300</v>
       </c>
       <c r="K33" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L33" s="3">
         <v>-300</v>
       </c>
       <c r="M33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O33" s="3">
         <v>-100</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-200</v>
       </c>
       <c r="P33" s="3">
         <v>-200</v>
       </c>
       <c r="Q33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2302,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F35" s="3">
         <v>-100</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>-300</v>
-      </c>
       <c r="I35" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J35" s="3">
         <v>-300</v>
       </c>
       <c r="K35" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L35" s="3">
         <v>-300</v>
       </c>
       <c r="M35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O35" s="3">
         <v>-100</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-200</v>
       </c>
       <c r="P35" s="3">
         <v>-200</v>
       </c>
       <c r="Q35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2459,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,40 +2483,42 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>0</v>
+      <c r="D41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
       </c>
       <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>400</v>
-      </c>
-      <c r="L41" s="3">
-        <v>700</v>
-      </c>
-      <c r="M41" s="3">
-        <v>800</v>
       </c>
       <c r="N41" s="3">
         <v>700</v>
@@ -2353,22 +2527,28 @@
         <v>800</v>
       </c>
       <c r="P41" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>800</v>
+      </c>
+      <c r="R41" s="3">
         <v>900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2388,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
@@ -2399,11 +2579,11 @@
       <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
+      <c r="M42" s="3">
+        <v>100</v>
+      </c>
+      <c r="N42" s="3">
+        <v>100</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
@@ -2414,35 +2594,41 @@
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>4</v>
       </c>
@@ -2455,11 +2641,11 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2479,31 +2665,37 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2517,8 +2709,8 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
+      <c r="O44" s="3">
+        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2526,8 +2718,8 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>4</v>
+      <c r="R44" s="3">
+        <v>0</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>4</v>
@@ -2535,22 +2727,28 @@
       <c r="T44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
@@ -2559,10 +2757,10 @@
         <v>100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2577,54 +2775,60 @@
         <v>0</v>
       </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
         <v>300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>700</v>
-      </c>
-      <c r="M46" s="3">
-        <v>900</v>
       </c>
       <c r="N46" s="3">
         <v>700</v>
@@ -2633,36 +2837,42 @@
         <v>900</v>
       </c>
       <c r="P46" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>900</v>
+      </c>
+      <c r="R46" s="3">
         <v>1000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
@@ -2688,11 +2898,11 @@
       <c r="O47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
+      <c r="P47" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>100</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
@@ -2703,8 +2913,14 @@
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2739,19 +2955,19 @@
         <v>0</v>
       </c>
       <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
+      <c r="R48" s="3">
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>4</v>
@@ -2759,8 +2975,14 @@
       <c r="T48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2801,22 +3023,28 @@
         <v>0</v>
       </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>100</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3099,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3161,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2941,11 +3181,11 @@
       <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -2971,11 +3211,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>4</v>
@@ -2983,8 +3223,14 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,16 +3285,22 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E54" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F54" s="3">
         <v>300</v>
@@ -3057,37 +3309,37 @@
         <v>200</v>
       </c>
       <c r="H54" s="3">
+        <v>300</v>
+      </c>
+      <c r="I54" s="3">
         <v>200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
+        <v>200</v>
+      </c>
+      <c r="K54" s="3">
         <v>300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>900</v>
-      </c>
-      <c r="M54" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N54" s="3">
-        <v>800</v>
       </c>
       <c r="O54" s="3">
         <v>1000</v>
       </c>
       <c r="P54" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q54" s="3">
         <v>1000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>4</v>
+      <c r="R54" s="3">
+        <v>1000</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>4</v>
@@ -3095,8 +3347,14 @@
       <c r="T54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3375,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,8 +3399,10 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3151,19 +3413,19 @@
         <v>0</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -3183,11 +3445,11 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>4</v>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>4</v>
@@ -3195,35 +3457,41 @@
       <c r="T57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>400</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
       </c>
       <c r="I58" s="3">
+        <v>500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>500</v>
+      </c>
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
@@ -3236,11 +3504,11 @@
       <c r="O58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3251,35 +3519,41 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="G59" s="3">
-        <v>100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
@@ -3295,11 +3569,11 @@
       <c r="P59" s="3">
         <v>0</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
+      <c r="Q59" s="3">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>4</v>
@@ -3307,35 +3581,41 @@
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>500</v>
+      </c>
+      <c r="F60" s="3">
         <v>400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>400</v>
-      </c>
-      <c r="F60" s="3">
-        <v>500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>600</v>
       </c>
       <c r="H60" s="3">
         <v>500</v>
       </c>
       <c r="I60" s="3">
+        <v>600</v>
+      </c>
+      <c r="J60" s="3">
+        <v>500</v>
+      </c>
+      <c r="K60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3">
-        <v>0</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3351,11 +3631,11 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>4</v>
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>4</v>
@@ -3363,8 +3643,14 @@
       <c r="T60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3419,16 +3705,22 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>4</v>
@@ -3436,14 +3728,14 @@
       <c r="G62" s="3">
         <v>0</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
@@ -3475,8 +3767,14 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3829,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3891,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,35 +3953,41 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>500</v>
+      </c>
+      <c r="F66" s="3">
         <v>400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>400</v>
-      </c>
-      <c r="F66" s="3">
-        <v>500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>600</v>
       </c>
       <c r="H66" s="3">
         <v>500</v>
       </c>
       <c r="I66" s="3">
+        <v>600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>500</v>
+      </c>
+      <c r="K66" s="3">
         <v>400</v>
       </c>
-      <c r="J66" s="3">
-        <v>0</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
       <c r="L66" s="3">
         <v>0</v>
       </c>
@@ -3687,11 +4003,11 @@
       <c r="P66" s="3">
         <v>0</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>4</v>
+      <c r="Q66" s="3">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3">
+        <v>0</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>4</v>
@@ -3699,8 +4015,14 @@
       <c r="T66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4043,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4101,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +4163,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4225,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4287,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-5700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-5600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-5600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-5500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-5400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-5100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-4700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-4400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-4100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-3800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-3700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-3600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4411,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4473,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,40 +4535,46 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F76" s="3">
         <v>-100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>600</v>
-      </c>
-      <c r="L76" s="3">
-        <v>800</v>
-      </c>
-      <c r="M76" s="3">
-        <v>1000</v>
       </c>
       <c r="N76" s="3">
         <v>800</v>
@@ -4211,13 +4583,13 @@
         <v>1000</v>
       </c>
       <c r="P76" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q76" s="3">
         <v>1000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>4</v>
+      <c r="R76" s="3">
+        <v>1000</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>4</v>
@@ -4225,8 +4597,14 @@
       <c r="T76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4659,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F81" s="3">
         <v>-100</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>-300</v>
-      </c>
       <c r="I81" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J81" s="3">
         <v>-300</v>
       </c>
       <c r="K81" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="L81" s="3">
         <v>-300</v>
       </c>
       <c r="M81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O81" s="3">
         <v>-100</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-200</v>
       </c>
       <c r="P81" s="3">
         <v>-200</v>
       </c>
       <c r="Q81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4816,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4476,8 +4874,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4936,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4998,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5060,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5122,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,31 +5184,37 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E89" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F89" s="3">
         <v>-200</v>
       </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H89" s="3">
         <v>-200</v>
       </c>
       <c r="I89" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="J89" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="K89" s="3">
         <v>-300</v>
@@ -4789,22 +5223,22 @@
         <v>-300</v>
       </c>
       <c r="M89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O89" s="3">
         <v>-100</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-300</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
       </c>
       <c r="Q89" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -4812,8 +5246,14 @@
       <c r="T89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,31 +5274,33 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4878,11 +5320,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
@@ -4890,8 +5332,14 @@
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5394,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,31 +5456,37 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="H94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -5041,25 +5501,31 @@
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,31 +5546,33 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5136,8 +5604,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5666,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5728,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,87 +5790,99 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
         <v>100</v>
       </c>
       <c r="F100" s="3">
+        <v>200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>100</v>
+      </c>
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>300</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
       </c>
       <c r="O100" s="3">
         <v>300</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>300</v>
+      </c>
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>4</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5416,8 +5914,14 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5425,51 +5929,57 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>900</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
         <v>0</v>
       </c>
     </row>
